--- a/data/trans_dic/IP31B_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>67,59%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,94; 74,82</t>
+          <t>61,96; 83,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,85; 84,81</t>
+          <t>49,25; 72,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,29; 77,65</t>
+          <t>59,81; 75,42</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,4; 48,92</t>
+          <t>32,85; 45,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,31; 46,61</t>
+          <t>36,2; 48,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 45,7</t>
+          <t>36,08; 45,01</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 29,88</t>
+          <t>24,59; 35,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,27; 37,27</t>
+          <t>18,69; 30,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,94; 32,13</t>
+          <t>23,67; 31,89</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 51,82</t>
+          <t>21,63; 33,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,03; 36,06</t>
+          <t>17,23; 26,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,91; 41,37</t>
+          <t>20,67; 28,4</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 43,52</t>
+          <t>29,95; 36,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,59; 39,0</t>
+          <t>26,9; 33,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,73; 39,02</t>
+          <t>29,32; 34,05</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62217</t>
+          <t>52530</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22873; 32950</t>
+          <t>23012; 31071</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28663; 38070</t>
+          <t>19983; 29311</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55389; 69048</t>
+          <t>46482; 58609</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67798</t>
+          <t>60195</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72427</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140225</t>
+          <t>121376</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57835; 77736</t>
+          <t>51094; 70024</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61506; 83563</t>
+          <t>52553; 70019</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125228; 154548</t>
+          <t>108499; 135339</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41400</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64952</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106352</t>
+          <t>102715</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32481; 51711</t>
+          <t>48710; 70978</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53158; 78415</t>
+          <t>32639; 52848</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91799; 123192</t>
+          <t>88221; 118894</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>82334</t>
+          <t>77758</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>87749</t>
+          <t>55283</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170083</t>
+          <t>133041</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56263; 141567</t>
+          <t>63199; 97262</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70229; 109995</t>
+          <t>43800; 67726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138268; 239208</t>
+          <t>112944; 155153</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>289</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>219727</t>
+          <t>225858</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>192703; 282508</t>
+          <t>204522; 250878</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>233608; 288414</t>
+          <t>165303; 203868</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>440688; 541957</t>
+          <t>380431; 441822</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31B_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>74,37%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61,39%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>67,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>61,96; 83,67</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>49,25; 72,23</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59,81; 75,42</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>38,7%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>42,14%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>40,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>32,85; 45,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36,2; 48,23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36,08; 45,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>24,59; 35,83</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18,69; 30,26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23,67; 31,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>26,61%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21,75%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>21,63; 33,28</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17,23; 26,65</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20,67; 28,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29,91%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>29,95; 36,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26,9; 33,17</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29,32; 34,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.7436905342035206</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6139361691079932</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6759407028807913</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>27618</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24912</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52530</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.619640039711011</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4924597408414889</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5981104142867794</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>23012; 31071</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>19983; 29311</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46482; 58609</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.8366570273058388</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7223304409138515</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7541648558733571</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3870181370950561</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4214156274427882</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4036244199498358</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>60195</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>61180</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>121376</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.3285001491726087</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.3619906911057002</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.3608049139279654</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>51094; 70024</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>52553; 70019</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>108499; 135339</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4502083315753381</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4822978200090124</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4500577214850198</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3043324373597474</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2429022878471743</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2755472974517909</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>60286</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42428</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>102715</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.245892896501072</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.186857531429262</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.2366651624742266</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>48710; 70978</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>32639; 52848</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>88221; 118894</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3583021255829194</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.3025585034336352</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3189486885343489</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2660948089601641</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2175215509660052</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2435005043898135</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>77758</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>55283</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.2162707920354213</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1723412441647453</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.2067173206078489</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>63199; 97262</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>43800; 67726</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>112944; 155153</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3328361382409022</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2664811434485976</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2839701735318259</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.330691749211116</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.2990732199520793</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3157160015919697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>225858</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>183803</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>409662</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.2994523635459768</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.2689715252792208</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.2931887174093058</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>204522; 250878</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>165303; 203868</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>380431; 441822</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3673235895481225</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.3317212280719505</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3405006069469989</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>27618</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>24912</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>52530</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>23012</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>19983</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>46482</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>31071</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>29311</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>58609</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>60195</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>61180</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>121376</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>51094</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>52553</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>108499</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>70024</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>70019</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>135339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>60286</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>42428</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>102715</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>48710</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>32639</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>88221</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>70978</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>52848</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>118894</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>77758</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>55283</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>133041</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>63199</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>43800</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>112944</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>97262</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>67726</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>155153</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>347</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>225858</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>183803</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>409662</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>204522</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>165303</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>380431</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>250878</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>203868</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>441822</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>